--- a/inferences/jesuita-entrada-Coimbra-cargos_tarefas.datas.xlsx
+++ b/inferences/jesuita-entrada-Coimbra-cargos_tarefas.datas.xlsx
@@ -1016,12 +1016,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1646</t>
         </is>
       </c>
     </row>
